--- a/Questionairs/Overview_Questionaires.xlsx
+++ b/Questionairs/Overview_Questionaires.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f2d186216cf91ab/Bidlung/University/M.S. Leiden University/M.S. Neuroscience (Research)/MAPP/Analysis/Github_Clone/MAPP/Questionairs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_F25DC773A252ABDACC104863A15F71365ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8246B09-3BD7-4482-A2BF-4A61DC6F3B4B}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC104863A15F71365ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3F6D3BF-7D16-4B2A-ABB7-1CAB2D799138}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="-17475" windowWidth="21210" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13770" yWindow="2595" windowWidth="13440" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Questionaire</t>
   </si>
@@ -121,6 +121,15 @@
   </si>
   <si>
     <t>differs (See next sheet!)</t>
+  </si>
+  <si>
+    <t>MEQ</t>
+  </si>
+  <si>
+    <t>PEQ</t>
+  </si>
+  <si>
+    <t>SLS</t>
   </si>
 </sst>
 </file>
@@ -156,9 +165,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="66" bestFit="1" customWidth="1"/>
@@ -525,7 +533,7 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -581,7 +589,7 @@
       <c r="C10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -595,8 +603,23 @@
       <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
